--- a/output/pdf_financials_xlsx/ATLA.xlsx
+++ b/output/pdf_financials_xlsx/ATLA.xlsx
@@ -2227,16 +2227,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.130817</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.136515</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.130817</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.130817</v>
       </c>
     </row>
     <row r="93">
@@ -2717,16 +2717,16 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.108011</v>
+        <v>0.003236</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.054</v>
+        <v>-0.323337</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.006169</v>
+        <v>0.002086</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>3.588626</v>
+        <v>3.58387</v>
       </c>
     </row>
     <row r="119">
@@ -3544,7 +3544,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3760,7 +3764,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>0.130817</v>
       </c>
@@ -4212,7 +4220,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>-0.104775</v>
       </c>

--- a/output/pdf_financials_xlsx/ATLA.xlsx
+++ b/output/pdf_financials_xlsx/ATLA.xlsx
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000628</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000617</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000625</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000447</v>
       </c>
     </row>
     <row r="13">
@@ -944,16 +944,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.297875</v>
+        <v>-0.298503</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.085879</v>
+        <v>-0.086496</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.076837</v>
+        <v>-0.077462</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.72307</v>
+        <v>-3.723517</v>
       </c>
     </row>
     <row r="28">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.297875</v>
+        <v>-0.298503</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.085879</v>
+        <v>-0.086496</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.076837</v>
+        <v>-0.077462</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.72307</v>
+        <v>-3.723517</v>
       </c>
     </row>
     <row r="30">
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.412708</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.009558000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.6e-05</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.150331</v>
       </c>
     </row>
     <row r="35">
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.412708</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.009558000000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.6e-05</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.150331</v>
       </c>
     </row>
     <row r="37">
@@ -1347,16 +1347,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.419993</v>
+        <v>0.007285</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.016013</v>
+        <v>0.006455</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.004158</v>
+        <v>0.004142</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.15456</v>
+        <v>0.004229</v>
       </c>
     </row>
     <row r="49">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -3338,7 +3338,11 @@
           <t>Reclamation deposits (Note 4)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>0.030792</v>
       </c>
@@ -4896,7 +4900,11 @@
           <t>Reclamation Deposit</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>-0.015792</v>
       </c>
@@ -5356,7 +5364,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">

--- a/output/pdf_financials_xlsx/ATLA.xlsx
+++ b/output/pdf_financials_xlsx/ATLA.xlsx
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.142114</v>
+        <v>0.151194</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.075097</v>
+        <v>0.083097</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.029719</v>
+        <v>0.037719</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.103025</v>
+        <v>0.110432</v>
       </c>
     </row>
     <row r="8">
@@ -5014,7 +5014,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>1.128</v>
       </c>
@@ -5128,7 +5132,11 @@
           <t>Directors’ fees (Note 5)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>0.00908</v>
       </c>
